--- a/data/LME_052/models/52_1_Sea_of_Okhotsk_NE_(1980).xlsx
+++ b/data/LME_052/models/52_1_Sea_of_Okhotsk_NE_(1980).xlsx
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -58175,14 +58175,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ok</t>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>IMPLAUSIBLE - up to 76x the trophic-chain estimate; the solve is near-singular for this model</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -58406,7 +58406,7 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>6 of 20 methods are flagged above. A flagged row is a property of this model under that method, not of the mapping; see model_health in the SPPR workbook.</t>
+          <t>7 of 20 methods are flagged above. A flagged row is a property of this model under that method, not of the mapping; see model_health in the SPPR workbook.</t>
         </is>
       </c>
     </row>
